--- a/蔬心兰.xlsx
+++ b/蔬心兰.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -441,30 +441,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>杭州市临平区临平第三中学梅堰校区学生食堂</t>
+          <t>一馆三中心食堂</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>杭州市临平区塘栖第三中学教师食堂</t>
+          <t>临平区中医院</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>杭州市临平区树兰实验学校中学学生(肉类)</t>
+          <t>临平区中西医结合医院食堂（新）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>杭州市临平区树兰实验学校中学学生(蔬菜类)</t>
+          <t>临平区政府食堂</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>杭州市临平区树兰实验学校教师(肉类)</t>
+          <t>临平市民之家食堂</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>区妇幼保健院食堂</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>塘栖行政服务中心</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
@@ -473,850 +483,1553 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>特级72度蓝蓝莓(约60个/斤)(斤)</t>
+          <t>万隆腊鸡腿(斤)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="n">
-        <v>7</v>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>鸡蛋面(斤)</t>
+          <t>丝瓜(斤)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>70</v>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>70</v>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>袋装五丰牛奶刀切(450g,18只)</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>14</v>
-      </c>
+          <t>兰州包心菜(斤)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>14</v>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>拇指年糕(斤)</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
+          <t>冬瓜(斤)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>27.8</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="n">
+        <v>47.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>板装祖名老豆腐(4kg)</t>
+          <t>冷鲜5:5猪肉末(斤)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="D6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪前排(斤)</t>
+          <t>冷鲜三黄鸡(去内脏)(斤)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n">
+        <v>43</v>
+      </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>10</v>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪肉带龙骨子排(斤)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>冷鲜全精肉丝(斤)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪肉全精后腿肉(斤)</t>
+          <t>冷鲜半片鸭(斤)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="n">
-        <v>50</v>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪肉精大排(斤)</t>
+          <t>冷鲜木头鸭(去内脏)(斤)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="n">
-        <v>40</v>
-      </c>
+      <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="n">
-        <v>40</v>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪肉精猪爪(5寸)(斤)</t>
+          <t>冷鲜本鸡(去内脏)(斤)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>24</v>
+      </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>10</v>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪肉中方五花肉(斤)</t>
+          <t>冷鲜牛毛肚(斤)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="n">
-        <v>85</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>110</v>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>热鲜猪9:1猪肉末(斤)</t>
+          <t>冷鲜猪前排(斤)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>35</v>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>冷鲜木头鸭(去内脏)(斤) / 冷鲜木头鸭(去内脏)(斤)(洋鸭)</t>
+          <t>冷鲜猪爪(斤)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="n">
-        <v>90</v>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="n">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>冷鲜本鸡(去内脏)(斤)</t>
+          <t>冷鲜猪肉中方五花肉(斤)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="n">
+        <v>37</v>
+      </c>
       <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="n">
-        <v>150</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="n">
-        <v>150</v>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>鲜牛肉牛腩(斤)</t>
+          <t>冷鲜猪肉五花肉片(斤)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="n">
-        <v>90</v>
-      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="n">
-        <v>90</v>
+        <v>12</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>牛排(斤)</t>
+          <t>冷鲜猪肉全精肉片(斤)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>15</v>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>杭味腊肠(斤)</t>
+          <t>冷鲜猪肉排(斤)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="n">
-        <v>10</v>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>箱装大成炸翅根(10kg)</t>
+          <t>冷鲜猪肉末(7:3)(斤)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
-      <c r="C19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="n">
+        <v>30</v>
+      </c>
       <c r="D19" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>箱装大成超厚鸡排(2.25kg*4)</t>
+          <t>冷鲜猪肉精品五花肉(斤)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>袋装大成奥尔良早餐腿排(1kg)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
+          <t>冷鲜猪肉精大排(斤)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="n">
-        <v>25</v>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>箱装大成琵琶腿(小)(10kg,80多个)</t>
+          <t>咸猪爪(斤)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>胡萝卜(斤)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
+          <t>大娃娃菜(斤)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="n">
-        <v>5</v>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>老生姜(斤) / 老生姜(斤)(老姜)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
+          <t>大尖椒(斤)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>娃娃菜(斤)</t>
+          <t>大白菜(斤)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
-      <c r="C25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="n">
-        <v>160</v>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="n">
-        <v>160</v>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>青菜(斤)</t>
+          <t>大红椒(斤)</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="n">
-        <v>10</v>
+      <c r="F26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>兰州包心菜(斤)</t>
+          <t>大馄饨皮(斤)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="n">
-        <v>80</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="n">
-        <v>90</v>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>上海青(斤)</t>
+          <t>小油豆腐(斤)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="n">
-        <v>220</v>
-      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="n">
-        <v>220</v>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>小葱(较细)(斤)</t>
+          <t>小番薯(斤)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="n">
-        <v>13</v>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>洋葱(斤)</t>
+          <t>小米椒(斤)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="n">
-        <v>20</v>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>青大蒜(斤)</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>小葱(较细)(斤)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="n">
-        <v>5</v>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>韭菜(斤)</t>
+          <t>小馄饨皮(斤)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="n">
-        <v>5</v>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>大蒜子(斤)</t>
+          <t>支装祖名豆奶(250ml)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="n">
-        <v>5</v>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>蒜苗(斤)</t>
+          <t>新鲜毛豆仁(斤)(去皮毛豆)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="n">
-        <v>20</v>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>西红柿(斤)(番茄)</t>
+          <t>新鲜香菇(斤)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="n">
-        <v>120</v>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="n">
-        <v>120</v>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>茄子(斤)</t>
+          <t>春笋干(斤)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="n">
-        <v>50</v>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="n">
-        <v>50</v>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>彩椒(斤)</t>
+          <t>普通花菜(斤)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="n">
-        <v>30</v>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>冬瓜(斤)</t>
+          <t>普通鸡蛋(斤)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="n">
+      <c r="C38" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="D38" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="n">
-        <v>100</v>
+        <v>150</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>老南瓜(斤)</t>
+          <t>本地毛毛菜(斤)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="n">
-        <v>15</v>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>日本嫩南瓜(斤)</t>
+          <t>本地芹菜(斤)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="n">
-        <v>30</v>
-      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="n">
-        <v>30</v>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>荷兰黄心大土豆(斤)</t>
+          <t>本地茄子(斤)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="n">
-        <v>120</v>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>新鲜香菇(斤)</t>
+          <t>毛毛菜(斤)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="n">
-        <v>3</v>
+      <c r="E42" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="n">
+        <v>139</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>去皮板栗肉(斤)</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
+          <t>毛芋艿(斤)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>20</v>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>咸榨菜头(斤)</t>
+          <t>河粉(斤)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="n">
-        <v>15</v>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>潮州酸菜(斤)</t>
+          <t>洋葱(斤)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="n">
-        <v>20</v>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>毛毛菜(斤)</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>海带丝(斤)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="n">
-        <v>40</v>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>松花菜(斤)</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>牛百叶(斤)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="n">
-        <v>60</v>
-      </c>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="n">
-        <v>110</v>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>草鱼(斤)</t>
+          <t>特级梅干菜(斤)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="n">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>花鲢(包头鱼)(斤)(包头鱼)</t>
+          <t>甜玉米棒(净)(斤)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>30</v>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>明虾(大)（约30-40只）(斤)</t>
+          <t>生菜(斤)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>20</v>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>白玉菇(斤)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>白萝卜(斤)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>白蘑菇(斤)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>盒装鸿光浪花大中华豆腐(6kg)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>粉西红柿(斤)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>老生姜(斤)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>老黄豆(大)(斤)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>胡萝卜(斤)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>茭白肉(斤)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>荷兰黄心大土豆(斤)</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>莴笋肉(斤)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>莴笋（带叶）(斤)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>袋装娃娃菜(包)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>袋装祖名薄千张(2kg)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>袋装西式方腿(400g)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>袋装鸿光浪花香干
+(1kg，约35片)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>西兰花(斤)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>西红柿(斤)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>长瓜(斤)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>青大蒜(斤)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>青螺丝椒(斤)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>青雪菜(斤)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>鞭笋(斤)(边笋)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>韭黄(斤)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>香蒿菜(斤)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>鲜糯玉米棒（去壳）(斤)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>鲜细面(斤)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>鸡蛋面(斤)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>鸭血(约250g/块)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>黄豆芽(斤)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
